--- a/tests/database/test_database.xlsx
+++ b/tests/database/test_database.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/u0065634/Documents/Software_projects/msi-quant/tests/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC0A8E1-84F7-D848-A871-295A76B56A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1A503F-408F-C141-98FA-D0ED827F4D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3600" yWindow="1160" windowWidth="30240" windowHeight="17780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="64">
   <si>
     <t>ID</t>
   </si>
@@ -46,30 +59,12 @@
     <t>M-2</t>
   </si>
   <si>
-    <t>PC 28:0</t>
-  </si>
-  <si>
-    <t>[C36H72NKPO8]+</t>
-  </si>
-  <si>
     <t>PC</t>
   </si>
   <si>
     <t>[M+K]+</t>
   </si>
   <si>
-    <t>PC 30:0</t>
-  </si>
-  <si>
-    <t>[C38H76NKPO8]+</t>
-  </si>
-  <si>
-    <t>PC 32:0</t>
-  </si>
-  <si>
-    <t>[C40H80NKPO8]+</t>
-  </si>
-  <si>
     <t>PC 32:1</t>
   </si>
   <si>
@@ -127,15 +122,9 @@
     <t>[M-H]-</t>
   </si>
   <si>
-    <t>PE 33:1 d7</t>
-  </si>
-  <si>
     <t>[M+Na]+</t>
   </si>
   <si>
-    <t>[C40H80NNaPO8]+</t>
-  </si>
-  <si>
     <t>[C40H78NNaPO8]+</t>
   </si>
   <si>
@@ -143,14 +132,108 @@
   </si>
   <si>
     <t>[C44H86NNaPO8]+</t>
+  </si>
+  <si>
+    <t>Carbons</t>
+  </si>
+  <si>
+    <t>Double bonds</t>
+  </si>
+  <si>
+    <t>Oxigens</t>
+  </si>
+  <si>
+    <t>[C41H73D7NNaPO8]+</t>
+  </si>
+  <si>
+    <t>[C40H76NNaPO8]+</t>
+  </si>
+  <si>
+    <t>[C42H80NNaPO8]+</t>
+  </si>
+  <si>
+    <t>[C44H84NNaPO8]+</t>
+  </si>
+  <si>
+    <t>PC 32:4</t>
+  </si>
+  <si>
+    <t>[C40H72NNaPO8]+</t>
+  </si>
+  <si>
+    <t>PC 34:4</t>
+  </si>
+  <si>
+    <t>[C42H76NNaPO8]+</t>
+  </si>
+  <si>
+    <t>PC 36:4</t>
+  </si>
+  <si>
+    <t>[C44H80NNaPO8]+</t>
+  </si>
+  <si>
+    <t>PC 38:4</t>
+  </si>
+  <si>
+    <t>[C46H84NNaPO8]+</t>
+  </si>
+  <si>
+    <t>[C41H74D7NPO8]+</t>
+  </si>
+  <si>
+    <t>[M+H]+</t>
+  </si>
+  <si>
+    <t>[C40H79NPO8]+</t>
+  </si>
+  <si>
+    <t>[C42H83NPO8]+</t>
+  </si>
+  <si>
+    <t>[C44H87NPO8]+</t>
+  </si>
+  <si>
+    <t>[C40H77NPO8]+</t>
+  </si>
+  <si>
+    <t>[C42H81NPO8]+</t>
+  </si>
+  <si>
+    <t>[C44H85NPO8]+</t>
+  </si>
+  <si>
+    <t>[C40H73NPO8]+</t>
+  </si>
+  <si>
+    <t>[C42H77NPO8]+</t>
+  </si>
+  <si>
+    <t>[C44H81NPO8]+</t>
+  </si>
+  <si>
+    <t>[C46H85NPO8]+</t>
+  </si>
+  <si>
+    <t>[C40H72NKPO8]+</t>
+  </si>
+  <si>
+    <t>[C42H76NKPO8]+</t>
+  </si>
+  <si>
+    <t>[C44H80NKPO8]+</t>
+  </si>
+  <si>
+    <t>[C46H84NKPO8]+</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.00000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -210,7 +293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -218,6 +301,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -530,7 +620,7 @@
     <col min="10" max="10" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -547,482 +637,1247 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
+      <c r="M1" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="5">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3">
-        <v>791.56925000000001</v>
+        <v>775.59531335300005</v>
       </c>
       <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
         <v>29</v>
       </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2">
+      <c r="G2">
+        <v>33</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="7"/>
+      <c r="M2">
         <v>1.5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3">
-        <v>716.46271306099993</v>
+        <v>754.53572606700004</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3">
+        <v>32</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="6">
+        <v>44.830086657729147</v>
+      </c>
+      <c r="K3" s="6">
+        <v>11.45794133889807</v>
+      </c>
+      <c r="L3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="4">
-        <v>40.447333231842137</v>
-      </c>
-      <c r="H3" s="4">
-        <v>16.829336779175499</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
       <c r="C4" s="3">
-        <v>744.49401318899993</v>
+        <v>782.56702619500004</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="4">
-        <v>42.656484180996998</v>
-      </c>
-      <c r="H4" s="4">
-        <v>17.735580521296651</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+      <c r="G4">
+        <v>34</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <v>47.039237606884001</v>
+      </c>
+      <c r="K4" s="6">
+        <v>12.461006719926329</v>
+      </c>
+      <c r="L4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3">
+        <v>810.59832632300004</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5">
+        <v>36</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6">
+        <v>49.248388556038869</v>
+      </c>
+      <c r="K5" s="6">
+        <v>13.51287558011609</v>
+      </c>
+      <c r="L5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="3">
-        <v>772.52531331699993</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="4">
-        <v>44.865635130151887</v>
-      </c>
-      <c r="H5" s="4">
-        <v>18.690627742579341</v>
-      </c>
-      <c r="I5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
       <c r="C6" s="3">
-        <v>770.50966325299999</v>
+        <v>752.52007600299999</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="4">
-        <v>44.842632484847641</v>
-      </c>
-      <c r="H6" s="4">
-        <v>18.680311428079541</v>
-      </c>
-      <c r="I6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+      <c r="G6">
+        <v>32</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6">
+        <v>44.807084012424937</v>
+      </c>
+      <c r="K6" s="6">
+        <v>11.447633201487299</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3">
-        <v>798.54096338099998</v>
+        <v>780.55137613099998</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="4">
-        <v>47.051783434002537</v>
-      </c>
-      <c r="H7" s="4">
-        <v>19.68365396536667</v>
-      </c>
-      <c r="I7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
+        <v>29</v>
+      </c>
+      <c r="G7">
+        <v>34</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6">
+        <v>47.016234961579833</v>
+      </c>
+      <c r="K7" s="6">
+        <v>12.45019041935849</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="5">
         <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="3">
-        <v>826.57226350899998</v>
+        <v>808.58267625899998</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="4">
-        <v>49.260934383157391</v>
-      </c>
-      <c r="H8" s="4">
-        <v>20.735799981815319</v>
-      </c>
-      <c r="I8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+      <c r="G8">
+        <v>36</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6">
+        <v>49.225385910734659</v>
+      </c>
+      <c r="K8" s="6">
+        <v>13.501551116391189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C9" s="3">
-        <v>768.49401318899993</v>
+        <v>748.48877587499999</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="4">
-        <v>44.819629839543452</v>
-      </c>
-      <c r="H9" s="4">
-        <v>18.670000404796671</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
+        <v>29</v>
+      </c>
+      <c r="G9">
+        <v>32</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6">
+        <v>44.76107872181651</v>
+      </c>
+      <c r="K9" s="6">
+        <v>11.4270328003165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" s="5">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C10" s="3">
-        <v>796.52531331699993</v>
+        <v>776.52007600299999</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="4">
-        <v>47.028780788698349</v>
-      </c>
-      <c r="H10" s="4">
-        <v>19.672834778926731</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+      <c r="G10">
+        <v>34</v>
+      </c>
+      <c r="H10">
+        <v>4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6">
+        <v>46.970229670971378</v>
+      </c>
+      <c r="K10" s="6">
+        <v>12.428573691873551</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="C11" s="3">
-        <v>824.55661344499993</v>
+        <v>804.55137613099998</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11">
+        <v>36</v>
+      </c>
+      <c r="H11">
+        <v>4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6">
+        <v>49.179380620126267</v>
+      </c>
+      <c r="K11" s="6">
+        <v>13.47891806259212</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" s="5">
         <v>10</v>
       </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="4">
-        <v>49.237931737853181</v>
-      </c>
-      <c r="H11" s="4">
-        <v>20.724472632218291</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C12" s="3">
-        <v>791.56925000000001</v>
+        <v>832.58267625899998</v>
       </c>
       <c r="D12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
         <v>29</v>
       </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>36</v>
-      </c>
-      <c r="J12">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G12">
+        <v>38</v>
+      </c>
+      <c r="H12">
+        <v>4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" s="6">
+        <v>51.388531569281113</v>
+      </c>
+      <c r="K12" s="6">
+        <v>14.5780659124722</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="3">
+        <v>753.61336871000003</v>
+      </c>
+      <c r="D13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13">
+        <v>33</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="M13">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" s="5">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="3">
+        <v>732.55378142399991</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14">
+        <v>32</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" s="6">
+        <v>44.841587980381227</v>
+      </c>
+      <c r="K14" s="6">
+        <v>11.463097391809789</v>
+      </c>
+      <c r="L14" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="3">
-        <v>756.55137613099998</v>
-      </c>
-      <c r="D13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="4">
-        <v>44.865635130151887</v>
-      </c>
-      <c r="H13" s="4">
-        <v>18.690627742579341</v>
-      </c>
-      <c r="I13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="3">
-        <v>754.53572606700004</v>
-      </c>
-      <c r="D14" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14" s="4">
-        <v>44.842632484847641</v>
-      </c>
-      <c r="H14" s="4">
-        <v>18.680311428079541</v>
-      </c>
-      <c r="I14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C15" s="3">
-        <v>782.56702619500004</v>
+        <v>760.58508155200002</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15">
+        <v>34</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" s="6">
+        <v>47.050738929536116</v>
+      </c>
+      <c r="K15" s="6">
+        <v>12.466416854416581</v>
+      </c>
+      <c r="L15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" s="5">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="3">
+        <v>788.61638168000002</v>
+      </c>
+      <c r="D16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16">
         <v>36</v>
       </c>
-      <c r="G15" s="4">
-        <v>47.051783434002537</v>
-      </c>
-      <c r="H15" s="4">
-        <v>19.68365396536667</v>
-      </c>
-      <c r="I15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" s="6">
+        <v>49.259889878690977</v>
+      </c>
+      <c r="K16" s="6">
+        <v>13.518539796184889</v>
+      </c>
+      <c r="L16" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="3">
-        <v>810.59832632300004</v>
-      </c>
-      <c r="D16" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="4">
-        <v>49.260934383157391</v>
-      </c>
-      <c r="H16" s="4">
-        <v>20.735799981815319</v>
-      </c>
-      <c r="I16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="3">
+        <v>730.53813135999997</v>
+      </c>
+      <c r="D17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17">
+        <v>32</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" s="6">
+        <v>44.81858533507706</v>
+      </c>
+      <c r="K17" s="6">
+        <v>11.45278660879058</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" s="5">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="3">
+        <v>758.56943148799996</v>
+      </c>
+      <c r="D18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18">
+        <v>34</v>
+      </c>
+      <c r="H18">
+        <v>2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18" s="6">
+        <v>47.027736284231928</v>
+      </c>
+      <c r="K18" s="6">
+        <v>12.4555979082403</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="3">
+        <v>786.60073161599996</v>
+      </c>
+      <c r="D19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19">
+        <v>36</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19" s="6">
+        <v>49.236887233386788</v>
+      </c>
+      <c r="K19" s="6">
+        <v>13.50721268685154</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" s="5">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="3">
+        <v>726.50683123199997</v>
+      </c>
+      <c r="D20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20">
+        <v>32</v>
+      </c>
+      <c r="H20">
+        <v>4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20" s="6">
+        <v>44.772580044468633</v>
+      </c>
+      <c r="K20" s="6">
+        <v>11.43218091640286</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="3">
+        <v>754.53813135999997</v>
+      </c>
+      <c r="D21" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21">
+        <v>34</v>
+      </c>
+      <c r="H21">
+        <v>4</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21" s="6">
+        <v>46.981730993623508</v>
+      </c>
+      <c r="K21" s="6">
+        <v>12.43397588953845</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" s="5">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="3">
+        <v>782.56943148799996</v>
+      </c>
+      <c r="D22" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>49</v>
+      </c>
+      <c r="G22">
+        <v>36</v>
+      </c>
+      <c r="H22">
+        <v>4</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22" s="6">
+        <v>49.19088194277839</v>
+      </c>
+      <c r="K22" s="6">
+        <v>13.484574341835559</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="3">
+        <v>810.60073161599996</v>
+      </c>
+      <c r="D23" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>49</v>
+      </c>
+      <c r="G23">
+        <v>38</v>
+      </c>
+      <c r="H23">
+        <v>4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23" s="6">
+        <v>51.400032891933243</v>
+      </c>
+      <c r="K23" s="6">
+        <v>14.58397627329418</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" s="5">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="3">
+        <v>791.56925000000001</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24">
+        <v>33</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="M24">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="3">
+        <v>770.50966325299999</v>
+      </c>
+      <c r="D25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25">
+        <v>32</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25" s="6">
+        <v>44.842632484847641</v>
+      </c>
+      <c r="K25" s="6">
+        <v>18.680311428079541</v>
+      </c>
+      <c r="L25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A26" s="5">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="3">
+        <v>798.54096338099998</v>
+      </c>
+      <c r="D26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26">
+        <v>34</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26" s="6">
+        <v>47.051783434002537</v>
+      </c>
+      <c r="K26" s="6">
+        <v>19.68365396536667</v>
+      </c>
+      <c r="L26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="3">
+        <v>826.57226350899998</v>
+      </c>
+      <c r="D27" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27">
+        <v>36</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27" s="6">
+        <v>49.260934383157391</v>
+      </c>
+      <c r="K27" s="6">
+        <v>20.735799981815319</v>
+      </c>
+      <c r="L27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A28" s="5">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="3">
+        <v>768.49401318899993</v>
+      </c>
+      <c r="D28" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28">
+        <v>32</v>
+      </c>
+      <c r="H28">
+        <v>2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28" s="6">
+        <v>44.819629839543452</v>
+      </c>
+      <c r="K28" s="6">
+        <v>18.670000404796671</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="3">
+        <v>796.52531331699993</v>
+      </c>
+      <c r="D29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29">
+        <v>34</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>47.028780788698349</v>
+      </c>
+      <c r="K29">
+        <v>19.672834778926731</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A30" s="5">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="3">
+        <v>824.55661344499993</v>
+      </c>
+      <c r="D30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30">
+        <v>36</v>
+      </c>
+      <c r="H30">
+        <v>2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>49.237931737853181</v>
+      </c>
+      <c r="K30">
+        <v>20.724472632218291</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="3">
+        <v>764.46271306099993</v>
+      </c>
+      <c r="D31" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G31">
+        <v>32</v>
+      </c>
+      <c r="H31">
+        <v>4</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31" s="6">
+        <v>44.77362454893504</v>
+      </c>
+      <c r="K31" s="6">
+        <v>18.64939423188164</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A32" s="5">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="3">
+        <v>792.49401318899993</v>
+      </c>
+      <c r="D32" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32">
+        <v>34</v>
+      </c>
+      <c r="H32">
+        <v>4</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32" s="6">
+        <v>46.982775498089893</v>
+      </c>
+      <c r="K32" s="6">
+        <v>19.65121227969756</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="C17" s="3">
+      <c r="B33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" s="3">
+        <v>820.52531331699993</v>
+      </c>
+      <c r="D33" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G33">
+        <v>36</v>
+      </c>
+      <c r="H33">
+        <v>4</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33" s="6">
+        <v>49.191926447244789</v>
+      </c>
+      <c r="K33" s="6">
+        <v>20.701833806675008</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="5">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="3">
+        <v>848.55661344499993</v>
+      </c>
+      <c r="D34" t="s">
+        <v>63</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>9</v>
+      </c>
+      <c r="G34">
+        <v>38</v>
+      </c>
+      <c r="H34">
+        <v>4</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34" s="6">
+        <v>51.401077396399643</v>
+      </c>
+      <c r="K34" s="6">
+        <v>21.801258812813948</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="3">
         <v>688.49227836199998</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D35" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35">
         <v>32</v>
       </c>
-      <c r="E17" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="4">
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35" s="4">
         <v>41.504858911344733</v>
       </c>
-      <c r="H17" s="4">
+      <c r="K35" s="4">
         <v>10.04007618304383</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="3">
-        <v>791.56925000000001</v>
-      </c>
-      <c r="D18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="J18">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="O2:X18">
-    <sortCondition ref="T2:T18"/>
-    <sortCondition ref="Q2:Q18"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="O1:U17">
+    <sortCondition ref="Q1:Q17"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/tests/database/test_database.xlsx
+++ b/tests/database/test_database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/u0065634/Documents/Software_projects/msi-quant/tests/database/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/u0065634/Documents/Software_projects/LipidQMap/tests/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2346C327-0B09-6B45-9F4F-10237ED9B5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D28BC8-6D86-1240-AAA1-5AF205BE8B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4660" yWindow="860" windowWidth="30240" windowHeight="17560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="860" windowWidth="30240" windowHeight="17560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="38">
   <si>
     <t>ID</t>
   </si>
@@ -141,6 +141,12 @@
   </si>
   <si>
     <t>Neutral Formula</t>
+  </si>
+  <si>
+    <t>PC 32:0</t>
+  </si>
+  <si>
+    <t>C40H80NPO8</t>
   </si>
 </sst>
 </file>
@@ -196,15 +202,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -510,316 +513,302 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5" customWidth="1"/>
-    <col min="5" max="5" width="20.5" customWidth="1"/>
-    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5" customWidth="1"/>
+    <col min="4" max="4" width="20.5" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
-        <v>0</v>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="4">
+      <c r="G2" s="3">
         <v>1.5</v>
       </c>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>1</v>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>36</v>
       </c>
       <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" s="1"/>
+      <c r="G3" s="3"/>
+      <c r="H3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="G4" s="3"/>
+      <c r="H4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+      <c r="G5" s="3"/>
+      <c r="H5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
+      <c r="G11" s="3"/>
+      <c r="H11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" t="s">
         <v>5</v>
       </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="4"/>
-      <c r="I8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="4"/>
-      <c r="I10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" t="s">
-        <v>4</v>
-      </c>
-      <c r="H11" s="4"/>
-      <c r="I11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
+      <c r="G13" s="3"/>
+      <c r="H13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" t="s">
-        <v>5</v>
-      </c>
-      <c r="H12" s="4"/>
-      <c r="I12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="D14" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="4"/>
+      <c r="G14" s="3"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K1:Q12">
-    <sortCondition ref="M1:M12"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J1:P13">
+    <sortCondition ref="L1:L13"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tests/database/test_database.xlsx
+++ b/tests/database/test_database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/u0065634/Documents/Software_projects/LipidQMap/tests/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D28BC8-6D86-1240-AAA1-5AF205BE8B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B068C2E-266D-704D-AAFE-1000C288ACC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="860" windowWidth="30240" windowHeight="17560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="42">
   <si>
     <t>ID</t>
   </si>
@@ -147,6 +147,18 @@
   </si>
   <si>
     <t>C40H80NPO8</t>
+  </si>
+  <si>
+    <t>SM 34:1</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>[M+H]+</t>
+  </si>
+  <si>
+    <t>C39H79N2O6P</t>
   </si>
 </sst>
 </file>
@@ -513,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -793,18 +805,33 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>10</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>33</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C15" t="s">
         <v>11</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D15" t="s">
         <v>12</v>
       </c>
-      <c r="G14" s="3"/>
+      <c r="G15" s="3"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J1:P13">

--- a/tests/database/test_database.xlsx
+++ b/tests/database/test_database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/u0065634/Documents/Software_projects/LipidQMap/tests/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B068C2E-266D-704D-AAFE-1000C288ACC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1D0FE0-9C79-254B-A4D3-9599F0FE7B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35460" yWindow="1560" windowWidth="30240" windowHeight="17460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="43">
   <si>
     <t>ID</t>
   </si>
@@ -159,12 +159,18 @@
   </si>
   <si>
     <t>C39H79N2O6P</t>
+  </si>
+  <si>
+    <t>M-4 Isotope</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00000000"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -214,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -223,6 +229,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -525,19 +532,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5" customWidth="1"/>
     <col min="4" max="4" width="20.5" customWidth="1"/>
     <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="7" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -554,16 +562,19 @@
         <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -578,12 +589,13 @@
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="3">
+      <c r="G2" s="1"/>
+      <c r="H2" s="3">
         <v>1.5</v>
       </c>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -599,13 +611,16 @@
       <c r="E3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="3"/>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="3"/>
+      <c r="I3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -621,12 +636,12 @@
       <c r="E4" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H4" s="3"/>
+      <c r="I4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -642,12 +657,12 @@
       <c r="E5" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="3"/>
+      <c r="I5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -663,12 +678,12 @@
       <c r="E6" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="3"/>
+      <c r="I6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -681,12 +696,12 @@
       <c r="D7" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="3"/>
+      <c r="I7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -699,12 +714,12 @@
       <c r="D8" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="3"/>
+      <c r="I8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -717,12 +732,12 @@
       <c r="D9" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="3"/>
+      <c r="I9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -735,12 +750,12 @@
       <c r="D10" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="3"/>
+      <c r="I10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -753,15 +768,15 @@
       <c r="D11" t="s">
         <v>21</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>3</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H11" s="3"/>
+      <c r="I11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -774,15 +789,15 @@
       <c r="D12" t="s">
         <v>21</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="3"/>
-      <c r="H12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H12" s="3"/>
+      <c r="I12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -795,15 +810,15 @@
       <c r="D13" t="s">
         <v>21</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="3"/>
-      <c r="H13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H13" s="3"/>
+      <c r="I13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -816,9 +831,9 @@
       <c r="D14" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -831,11 +846,17 @@
       <c r="D15" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H17" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J1:P13">
-    <sortCondition ref="L1:L13"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K1:Q13">
+    <sortCondition ref="M1:M13"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tests/database/test_database.xlsx
+++ b/tests/database/test_database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/u0065634/Documents/Software_projects/LipidQMap/tests/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1D0FE0-9C79-254B-A4D3-9599F0FE7B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960F22E6-2DEB-EB4A-A2BE-307DCDA98479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-35460" yWindow="1560" windowWidth="30240" windowHeight="17460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="44">
   <si>
     <t>ID</t>
   </si>
@@ -162,6 +162,9 @@
   </si>
   <si>
     <t>M-4 Isotope</t>
+  </si>
+  <si>
+    <t>IS standard</t>
   </si>
 </sst>
 </file>
@@ -532,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -541,11 +544,12 @@
     <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" customWidth="1"/>
     <col min="7" max="7" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1640625" customWidth="1"/>
+    <col min="9" max="9" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -567,14 +571,17 @@
       <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -590,12 +597,15 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="3">
+      <c r="H2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3">
         <v>1.5</v>
       </c>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -615,12 +625,15 @@
         <v>6</v>
       </c>
       <c r="G3" s="1"/>
-      <c r="H3" s="3"/>
-      <c r="I3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -636,12 +649,15 @@
       <c r="E4" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -657,12 +673,15 @@
       <c r="E5" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -678,12 +697,15 @@
       <c r="E6" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -696,12 +718,15 @@
       <c r="D7" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -714,12 +739,15 @@
       <c r="D8" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -732,12 +760,15 @@
       <c r="D9" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -750,12 +781,15 @@
       <c r="D10" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -771,12 +805,15 @@
       <c r="G11" t="s">
         <v>3</v>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -792,12 +829,15 @@
       <c r="G12" t="s">
         <v>4</v>
       </c>
-      <c r="H12" s="3"/>
-      <c r="I12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3"/>
+      <c r="J12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -813,12 +853,15 @@
       <c r="G13" t="s">
         <v>5</v>
       </c>
-      <c r="H13" s="3"/>
-      <c r="I13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -831,9 +874,12 @@
       <c r="D14" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -846,17 +892,20 @@
       <c r="D15" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H17" s="4"/>
+      <c r="H15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I17" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K1:Q13">
-    <sortCondition ref="M1:M13"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="L1:R13">
+    <sortCondition ref="N1:N13"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tests/database/test_database.xlsx
+++ b/tests/database/test_database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/u0065634/Documents/Software_projects/LipidQMap/tests/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960F22E6-2DEB-EB4A-A2BE-307DCDA98479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBD9EEE-85B0-DD40-BA44-E69BCFB55213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-35460" yWindow="1560" windowWidth="30240" windowHeight="17460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,9 +89,6 @@
     <t>IS</t>
   </si>
   <si>
-    <t>IS amount (pmol / mm2)</t>
-  </si>
-  <si>
     <t>M-2 Isotope</t>
   </si>
   <si>
@@ -164,7 +161,10 @@
     <t>M-4 Isotope</t>
   </si>
   <si>
-    <t>IS standard</t>
+    <t>Is standard</t>
+  </si>
+  <si>
+    <t>Standard amount (pmol / mm2)</t>
   </si>
 </sst>
 </file>
@@ -554,28 +554,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>17</v>
@@ -586,13 +586,13 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -607,16 +607,16 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
         <v>36</v>
       </c>
-      <c r="B3" t="s">
-        <v>37</v>
-      </c>
       <c r="C3" t="s">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
         <v>3</v>
@@ -638,13 +638,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -662,13 +662,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -686,13 +686,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -710,13 +710,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H7" s="1" t="b">
         <v>0</v>
@@ -731,13 +731,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H8" s="1" t="b">
         <v>0</v>
@@ -752,13 +752,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H9" s="1" t="b">
         <v>0</v>
@@ -773,13 +773,13 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H10" s="1" t="b">
         <v>0</v>
@@ -794,13 +794,13 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G11" t="s">
         <v>3</v>
@@ -818,13 +818,13 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G12" t="s">
         <v>4</v>
@@ -842,13 +842,13 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G13" t="s">
         <v>5</v>
@@ -863,16 +863,16 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
         <v>38</v>
       </c>
-      <c r="B14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>39</v>
-      </c>
-      <c r="D14" t="s">
-        <v>40</v>
       </c>
       <c r="H14" s="1" t="b">
         <v>0</v>
@@ -884,7 +884,7 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
